--- a/VerveStacks_MAR_grids_kan10/vt_vervestacks_MAR_v1.xlsx
+++ b/VerveStacks_MAR_grids_kan10/vt_vervestacks_MAR_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MAR_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A2F5CB1-2537-4ADC-8924-5E5D1F9E2B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDEB82D5-0D84-479A-9575-DFACDFD79460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{14D81CED-9322-499C-B783-24C867063AA8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8D3086B6-B3AE-46D4-A921-C8385B604515}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1477,7 +1477,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CCE35F-6A60-49E4-BC33-4F5BFB49642B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C22387C-75FC-4D0B-9DF7-2F9B584044DD}">
   <dimension ref="B9:V37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3231,7 +3231,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C258BCEA-A33C-4569-9184-9CD25D615F76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50EEFA07-D23B-46A1-9231-5F9E935A0841}">
   <dimension ref="B9:W53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5926,7 +5926,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F0E1B9-F73C-487C-A830-BF8065C4F472}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A78D306C-24B6-43DD-8488-548E71C2C760}">
   <dimension ref="B9:W108"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8925,7 +8925,7 @@
         <v>15</v>
       </c>
       <c r="S61" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="T61" t="s">
         <v>155</v>
@@ -8987,7 +8987,7 @@
         <v>15</v>
       </c>
       <c r="S62" t="s">
-        <v>154</v>
+        <v>205</v>
       </c>
       <c r="T62" t="s">
         <v>155</v>
@@ -9111,7 +9111,7 @@
         <v>15</v>
       </c>
       <c r="S64" t="s">
-        <v>154</v>
+        <v>205</v>
       </c>
       <c r="T64" t="s">
         <v>155</v>
@@ -9173,7 +9173,7 @@
         <v>15</v>
       </c>
       <c r="S65" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="T65" t="s">
         <v>155</v>
@@ -9793,7 +9793,7 @@
         <v>15</v>
       </c>
       <c r="S75" t="s">
-        <v>154</v>
+        <v>205</v>
       </c>
       <c r="T75" t="s">
         <v>155</v>
@@ -9855,7 +9855,7 @@
         <v>15</v>
       </c>
       <c r="S76" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="T76" t="s">
         <v>155</v>
@@ -10392,7 +10392,7 @@
         <v>33</v>
       </c>
       <c r="N85">
-        <v>0.22592146020869974</v>
+        <v>0.22592146020869977</v>
       </c>
       <c r="P85" t="s">
         <v>153</v>
@@ -10445,7 +10445,7 @@
         <v>33</v>
       </c>
       <c r="N86">
-        <v>0.22592146020869974</v>
+        <v>0.22592146020869977</v>
       </c>
       <c r="P86" t="s">
         <v>153</v>
@@ -10498,7 +10498,7 @@
         <v>33</v>
       </c>
       <c r="N87">
-        <v>0.22592146020869974</v>
+        <v>0.22592146020869977</v>
       </c>
       <c r="P87" t="s">
         <v>153</v>
@@ -10758,7 +10758,7 @@
         <v>15</v>
       </c>
       <c r="S91" t="s">
-        <v>154</v>
+        <v>205</v>
       </c>
       <c r="T91" t="s">
         <v>155</v>
@@ -10820,7 +10820,7 @@
         <v>15</v>
       </c>
       <c r="S92" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="T92" t="s">
         <v>155</v>
@@ -11575,7 +11575,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B78F5B-B5FF-44A5-BD7B-1B25E0B8E36F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0267D996-357B-4F0E-90A9-129BD79C069A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
